--- a/outputs_MC/MC_inversion_results.xlsx
+++ b/outputs_MC/MC_inversion_results.xlsx
@@ -463,19 +463,19 @@
         <v>51</v>
       </c>
       <c r="C2" t="n">
-        <v>10.39903664829497</v>
+        <v>10.33726227861351</v>
       </c>
       <c r="D2" t="n">
-        <v>5.468949557101283</v>
+        <v>5.486424466838876</v>
       </c>
       <c r="E2" t="n">
-        <v>34.38012929558153</v>
+        <v>34.49189638493051</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -494,13 +494,13 @@
         <v>8.151896700162341</v>
       </c>
       <c r="E3" t="n">
-        <v>34.03017557928028</v>
+        <v>34.02932280114263</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -519,13 +519,13 @@
         <v>16.40604690583692</v>
       </c>
       <c r="E4" t="n">
-        <v>35.07702279573631</v>
+        <v>35.07902936825285</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -544,13 +544,13 @@
         <v>42.63480550689824</v>
       </c>
       <c r="E5" t="n">
-        <v>33.6080890704313</v>
+        <v>33.61813140548694</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -569,13 +569,13 @@
         <v>34.73653605652661</v>
       </c>
       <c r="E6" t="n">
-        <v>34.2675340242229</v>
+        <v>34.26878044944451</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -588,19 +588,19 @@
         <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>11.03858945173816</v>
+        <v>11.02679053001423</v>
       </c>
       <c r="D7" t="n">
-        <v>5.441345458495776</v>
+        <v>5.715695884247348</v>
       </c>
       <c r="E7" t="n">
-        <v>35.80171814067216</v>
+        <v>35.78136720655654</v>
       </c>
       <c r="F7" t="n">
-        <v>4.422718151771881</v>
+        <v>4.409631521254815</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -619,13 +619,13 @@
         <v>9.166197403466033</v>
       </c>
       <c r="E8" t="n">
-        <v>36.31013029787</v>
+        <v>36.30917021182518</v>
       </c>
       <c r="F8" t="n">
-        <v>5.309436163671582</v>
+        <v>5.309804719444602</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -644,13 +644,13 @@
         <v>13.56171640019001</v>
       </c>
       <c r="E9" t="n">
-        <v>35.13354730712815</v>
+        <v>35.13352604790742</v>
       </c>
       <c r="F9" t="n">
-        <v>4.287335035795541</v>
+        <v>4.287349899854081</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -669,13 +669,13 @@
         <v>25.15402768456995</v>
       </c>
       <c r="E10" t="n">
-        <v>34.89543419972706</v>
+        <v>34.89666700126604</v>
       </c>
       <c r="F10" t="n">
-        <v>4.314179058713993</v>
+        <v>4.313984129324608</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -694,13 +694,13 @@
         <v>27.43385805208527</v>
       </c>
       <c r="E11" t="n">
-        <v>34.62208827077563</v>
+        <v>34.62201701526037</v>
       </c>
       <c r="F11" t="n">
-        <v>3.394094295138477</v>
+        <v>3.394140590260294</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -719,13 +719,13 @@
         <v>6.810353209634561</v>
       </c>
       <c r="E12" t="n">
-        <v>38.71912782309562</v>
+        <v>38.71920452916503</v>
       </c>
       <c r="F12" t="n">
-        <v>7.497874514335442</v>
+        <v>7.497743176835728</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -744,13 +744,13 @@
         <v>10.33967452044064</v>
       </c>
       <c r="E13" t="n">
-        <v>36.52982591578074</v>
+        <v>36.528996524089</v>
       </c>
       <c r="F13" t="n">
-        <v>8.670724365585331</v>
+        <v>8.671365756030189</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -769,13 +769,13 @@
         <v>21.38613234774553</v>
       </c>
       <c r="E14" t="n">
-        <v>35.41756854824627</v>
+        <v>35.4184783588971</v>
       </c>
       <c r="F14" t="n">
-        <v>6.43120873100091</v>
+        <v>6.429696926939797</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -794,13 +794,13 @@
         <v>40.10591335563417</v>
       </c>
       <c r="E15" t="n">
-        <v>35.6793520414197</v>
+        <v>35.68079838117591</v>
       </c>
       <c r="F15" t="n">
-        <v>6.827844345817711</v>
+        <v>6.827389030443301</v>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -819,10 +819,10 @@
         <v>42.24441379816785</v>
       </c>
       <c r="E16" t="n">
-        <v>35.95084775244327</v>
+        <v>35.95039119261897</v>
       </c>
       <c r="F16" t="n">
-        <v>6.784619807918563</v>
+        <v>6.784955731289035</v>
       </c>
       <c r="G16" t="n">
         <v>8</v>
@@ -844,13 +844,13 @@
         <v>13.05962750207234</v>
       </c>
       <c r="E17" t="n">
-        <v>39.06108099951285</v>
+        <v>39.06259670734558</v>
       </c>
       <c r="F17" t="n">
-        <v>11.72714984336134</v>
+        <v>11.72681387725577</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -869,10 +869,10 @@
         <v>15.5663811536283</v>
       </c>
       <c r="E18" t="n">
-        <v>38.00815751544305</v>
+        <v>38.00931024517998</v>
       </c>
       <c r="F18" t="n">
-        <v>11.91586287601344</v>
+        <v>11.91231518407809</v>
       </c>
       <c r="G18" t="n">
         <v>8</v>
@@ -894,13 +894,13 @@
         <v>23.41993817384129</v>
       </c>
       <c r="E19" t="n">
-        <v>37.86560842562736</v>
+        <v>37.86614265368372</v>
       </c>
       <c r="F19" t="n">
-        <v>11.40812158699751</v>
+        <v>11.40782008838713</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -919,10 +919,10 @@
         <v>30.03737087950805</v>
       </c>
       <c r="E20" t="n">
-        <v>38.34267918636287</v>
+        <v>38.34212925040561</v>
       </c>
       <c r="F20" t="n">
-        <v>12.46529237021079</v>
+        <v>12.46660867371703</v>
       </c>
       <c r="G20" t="n">
         <v>10</v>
@@ -944,13 +944,13 @@
         <v>28.23000034407487</v>
       </c>
       <c r="E21" t="n">
-        <v>36.43591873194169</v>
+        <v>36.43725123534178</v>
       </c>
       <c r="F21" t="n">
-        <v>9.152611457943935</v>
+        <v>9.151759116290034</v>
       </c>
       <c r="G21" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -969,13 +969,13 @@
         <v>9.781814612989319</v>
       </c>
       <c r="E22" t="n">
-        <v>39.71991432836267</v>
+        <v>40</v>
       </c>
       <c r="F22" t="n">
-        <v>14.91856097225844</v>
+        <v>14.64747889472163</v>
       </c>
       <c r="G22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -994,13 +994,13 @@
         <v>19.7554869439188</v>
       </c>
       <c r="E23" t="n">
-        <v>39.67609739377755</v>
+        <v>39.78825281059851</v>
       </c>
       <c r="F23" t="n">
-        <v>13.21671143625188</v>
+        <v>13.19978941141515</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -1019,13 +1019,13 @@
         <v>38.37310806676264</v>
       </c>
       <c r="E24" t="n">
-        <v>39.75693671106172</v>
+        <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>13.75363799493093</v>
+        <v>13.6595168856354</v>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -1044,13 +1044,13 @@
         <v>51.34161955012367</v>
       </c>
       <c r="E25" t="n">
-        <v>39.12243878116794</v>
+        <v>39.12245155770542</v>
       </c>
       <c r="F25" t="n">
-        <v>12.94214592328223</v>
+        <v>12.94216841517408</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -1069,13 +1069,13 @@
         <v>58.02220888766763</v>
       </c>
       <c r="E26" t="n">
-        <v>38.13817757280207</v>
+        <v>38.13973715585971</v>
       </c>
       <c r="F26" t="n">
-        <v>11.59598051618767</v>
+        <v>11.59327038582531</v>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
